--- a/原始数据/低空经济测度指标/交通运输、仓储和邮政业增加值 (亿元).xlsx
+++ b/原始数据/低空经济测度指标/交通运输、仓储和邮政业增加值 (亿元).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="356">
   <si>
     <t>数据库：分省年度数据</t>
   </si>
@@ -19,18 +19,12 @@
     <t xml:space="preserve">指标：交通运输、仓储和邮政业增加值 (亿元) </t>
   </si>
   <si>
-    <t>时间：</t>
+    <t>时间：2014年-2023年</t>
   </si>
   <si>
     <t>地区</t>
   </si>
   <si>
-    <t>2025年</t>
-  </si>
-  <si>
-    <t>2024年</t>
-  </si>
-  <si>
     <t>2023年</t>
   </si>
   <si>
@@ -55,15 +49,15 @@
     <t>2016年</t>
   </si>
   <si>
+    <t>2015年</t>
+  </si>
+  <si>
+    <t>2014年</t>
+  </si>
+  <si>
     <t>北京市</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>1240.3</t>
-  </si>
-  <si>
     <t>1122.4</t>
   </si>
   <si>
@@ -88,12 +82,15 @@
     <t>793.4</t>
   </si>
   <si>
+    <t>742.3</t>
+  </si>
+  <si>
+    <t>729.9</t>
+  </si>
+  <si>
     <t>天津市</t>
   </si>
   <si>
-    <t>951.8</t>
-  </si>
-  <si>
     <t>907.7</t>
   </si>
   <si>
@@ -118,12 +115,15 @@
     <t>693.1</t>
   </si>
   <si>
+    <t>673.4</t>
+  </si>
+  <si>
+    <t>689.8</t>
+  </si>
+  <si>
     <t>河北省</t>
   </si>
   <si>
-    <t>3566.5</t>
-  </si>
-  <si>
     <t>3501.2</t>
   </si>
   <si>
@@ -148,12 +148,15 @@
     <t>2427.1</t>
   </si>
   <si>
+    <t>2416.1</t>
+  </si>
+  <si>
+    <t>2350.0</t>
+  </si>
+  <si>
     <t>山西省</t>
   </si>
   <si>
-    <t>1427.8</t>
-  </si>
-  <si>
     <t>1470.4</t>
   </si>
   <si>
@@ -178,12 +181,15 @@
     <t>750.5</t>
   </si>
   <si>
+    <t>726.1</t>
+  </si>
+  <si>
+    <t>648.6</t>
+  </si>
+  <si>
     <t>内蒙古自治区</t>
   </si>
   <si>
-    <t>1582.7</t>
-  </si>
-  <si>
     <t>1538.3</t>
   </si>
   <si>
@@ -208,12 +214,15 @@
     <t>983.4</t>
   </si>
   <si>
+    <t>943.0</t>
+  </si>
+  <si>
+    <t>916.6</t>
+  </si>
+  <si>
     <t>辽宁省</t>
   </si>
   <si>
-    <t>1785.0</t>
-  </si>
-  <si>
     <t>1581.9</t>
   </si>
   <si>
@@ -238,12 +247,15 @@
     <t>1208.8</t>
   </si>
   <si>
+    <t>1053.7</t>
+  </si>
+  <si>
+    <t>960.5</t>
+  </si>
+  <si>
     <t>吉林省</t>
   </si>
   <si>
-    <t>934.8</t>
-  </si>
-  <si>
     <t>898.6</t>
   </si>
   <si>
@@ -268,12 +280,15 @@
     <t>541.9</t>
   </si>
   <si>
+    <t>520.5</t>
+  </si>
+  <si>
+    <t>517.6</t>
+  </si>
+  <si>
     <t>黑龙江省</t>
   </si>
   <si>
-    <t>1101.8</t>
-  </si>
-  <si>
     <t>1023.8</t>
   </si>
   <si>
@@ -298,12 +313,15 @@
     <t>465.7</t>
   </si>
   <si>
+    <t>436.5</t>
+  </si>
+  <si>
+    <t>429.6</t>
+  </si>
+  <si>
     <t>上海市</t>
   </si>
   <si>
-    <t>2003.0</t>
-  </si>
-  <si>
     <t>1721.9</t>
   </si>
   <si>
@@ -328,12 +346,15 @@
     <t>1259.6</t>
   </si>
   <si>
+    <t>1148.0</t>
+  </si>
+  <si>
+    <t>1067.0</t>
+  </si>
+  <si>
     <t>江苏省</t>
   </si>
   <si>
-    <t>5158.8</t>
-  </si>
-  <si>
     <t>4897.7</t>
   </si>
   <si>
@@ -358,12 +379,15 @@
     <t>2553.9</t>
   </si>
   <si>
+    <t>2452.9</t>
+  </si>
+  <si>
+    <t>2610.3</t>
+  </si>
+  <si>
     <t>浙江省</t>
   </si>
   <si>
-    <t>2880.4</t>
-  </si>
-  <si>
     <t>2684.4</t>
   </si>
   <si>
@@ -388,12 +412,15 @@
     <t>1618.8</t>
   </si>
   <si>
+    <t>1511.4</t>
+  </si>
+  <si>
+    <t>1393.6</t>
+  </si>
+  <si>
     <t>安徽省</t>
   </si>
   <si>
-    <t>2917.2</t>
-  </si>
-  <si>
     <t>2848.0</t>
   </si>
   <si>
@@ -418,12 +445,15 @@
     <t>1475.0</t>
   </si>
   <si>
+    <t>1386.9</t>
+  </si>
+  <si>
+    <t>1360.6</t>
+  </si>
+  <si>
     <t>福建省</t>
   </si>
   <si>
-    <t>1885.7</t>
-  </si>
-  <si>
     <t>1734.2</t>
   </si>
   <si>
@@ -448,12 +478,15 @@
     <t>1191.9</t>
   </si>
   <si>
+    <t>1117.1</t>
+  </si>
+  <si>
+    <t>1045.3</t>
+  </si>
+  <si>
     <t>江西省</t>
   </si>
   <si>
-    <t>1412.7</t>
-  </si>
-  <si>
     <t>1355.0</t>
   </si>
   <si>
@@ -478,12 +511,15 @@
     <t>828.2</t>
   </si>
   <si>
+    <t>760.4</t>
+  </si>
+  <si>
+    <t>715.9</t>
+  </si>
+  <si>
     <t>山东省</t>
   </si>
   <si>
-    <t>4459.8</t>
-  </si>
-  <si>
     <t>4256.0</t>
   </si>
   <si>
@@ -508,12 +544,15 @@
     <t>2683.8</t>
   </si>
   <si>
+    <t>2453.9</t>
+  </si>
+  <si>
+    <t>2301.3</t>
+  </si>
+  <si>
     <t>河南省</t>
   </si>
   <si>
-    <t>3340.9</t>
-  </si>
-  <si>
     <t>3110.5</t>
   </si>
   <si>
@@ -538,12 +577,15 @@
     <t>2230.4</t>
   </si>
   <si>
+    <t>2048.7</t>
+  </si>
+  <si>
+    <t>1903.7</t>
+  </si>
+  <si>
     <t>湖北省</t>
   </si>
   <si>
-    <t>3119.3</t>
-  </si>
-  <si>
     <t>2847.1</t>
   </si>
   <si>
@@ -568,12 +610,15 @@
     <t>1665.8</t>
   </si>
   <si>
+    <t>1560.0</t>
+  </si>
+  <si>
+    <t>1464.6</t>
+  </si>
+  <si>
     <t>湖南省</t>
   </si>
   <si>
-    <t>2531.5</t>
-  </si>
-  <si>
     <t>2394.8</t>
   </si>
   <si>
@@ -598,12 +643,15 @@
     <t>1320.3</t>
   </si>
   <si>
+    <t>1261.4</t>
+  </si>
+  <si>
+    <t>1193.2</t>
+  </si>
+  <si>
     <t>广东省</t>
   </si>
   <si>
-    <t>5106.1</t>
-  </si>
-  <si>
     <t>4904.2</t>
   </si>
   <si>
@@ -628,12 +676,15 @@
     <t>2896.1</t>
   </si>
   <si>
+    <t>2680.5</t>
+  </si>
+  <si>
+    <t>2507.8</t>
+  </si>
+  <si>
     <t>广西壮族自治区</t>
   </si>
   <si>
-    <t>1115.4</t>
-  </si>
-  <si>
     <t>1075.3</t>
   </si>
   <si>
@@ -658,12 +709,15 @@
     <t>742.7</t>
   </si>
   <si>
+    <t>694.5</t>
+  </si>
+  <si>
+    <t>628.7</t>
+  </si>
+  <si>
     <t>海南省</t>
   </si>
   <si>
-    <t>330.4</t>
-  </si>
-  <si>
     <t>290.7</t>
   </si>
   <si>
@@ -688,12 +742,15 @@
     <t>189.7</t>
   </si>
   <si>
+    <t>177.7</t>
+  </si>
+  <si>
+    <t>151.1</t>
+  </si>
+  <si>
     <t>重庆市</t>
   </si>
   <si>
-    <t>1379.6</t>
-  </si>
-  <si>
     <t>1345.4</t>
   </si>
   <si>
@@ -718,12 +775,15 @@
     <t>782.4</t>
   </si>
   <si>
+    <t>731.0</t>
+  </si>
+  <si>
+    <t>685.7</t>
+  </si>
+  <si>
     <t>四川省</t>
   </si>
   <si>
-    <t>2612.4</t>
-  </si>
-  <si>
     <t>2558.1</t>
   </si>
   <si>
@@ -748,12 +808,15 @@
     <t>1126.3</t>
   </si>
   <si>
+    <t>948.1</t>
+  </si>
+  <si>
+    <t>870.8</t>
+  </si>
+  <si>
     <t>贵州省</t>
   </si>
   <si>
-    <t>907.2</t>
-  </si>
-  <si>
     <t>826.2</t>
   </si>
   <si>
@@ -778,12 +841,15 @@
     <t>506.7</t>
   </si>
   <si>
+    <t>457.7</t>
+  </si>
+  <si>
+    <t>424.9</t>
+  </si>
+  <si>
     <t>云南省</t>
   </si>
   <si>
-    <t>1395.8</t>
-  </si>
-  <si>
     <t>1319.0</t>
   </si>
   <si>
@@ -808,12 +874,12 @@
     <t>745.3</t>
   </si>
   <si>
+    <t>595.8</t>
+  </si>
+  <si>
     <t>西藏自治区</t>
   </si>
   <si>
-    <t>80.7</t>
-  </si>
-  <si>
     <t>76.0</t>
   </si>
   <si>
@@ -838,12 +904,15 @@
     <t>37.9</t>
   </si>
   <si>
+    <t>37.8</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
     <t>陕西省</t>
   </si>
   <si>
-    <t>1527.6</t>
-  </si>
-  <si>
     <t>1442.9</t>
   </si>
   <si>
@@ -868,12 +937,15 @@
     <t>885.3</t>
   </si>
   <si>
+    <t>809.2</t>
+  </si>
+  <si>
+    <t>758.7</t>
+  </si>
+  <si>
     <t>甘肃省</t>
   </si>
   <si>
-    <t>695.5</t>
-  </si>
-  <si>
     <t>639.7</t>
   </si>
   <si>
@@ -898,12 +970,15 @@
     <t>344.9</t>
   </si>
   <si>
+    <t>343.4</t>
+  </si>
+  <si>
+    <t>346.4</t>
+  </si>
+  <si>
     <t>青海省</t>
   </si>
   <si>
-    <t>177.7</t>
-  </si>
-  <si>
     <t>169.3</t>
   </si>
   <si>
@@ -928,12 +1003,15 @@
     <t>108.0</t>
   </si>
   <si>
+    <t>101.1</t>
+  </si>
+  <si>
+    <t>98.5</t>
+  </si>
+  <si>
     <t>宁夏回族自治区</t>
   </si>
   <si>
-    <t>227.1</t>
-  </si>
-  <si>
     <t>219.9</t>
   </si>
   <si>
@@ -958,12 +1036,15 @@
     <t>188.7</t>
   </si>
   <si>
+    <t>184.4</t>
+  </si>
+  <si>
+    <t>184.9</t>
+  </si>
+  <si>
     <t>新疆维吾尔自治区</t>
   </si>
   <si>
-    <t>1167.6</t>
-  </si>
-  <si>
     <t>1120.3</t>
   </si>
   <si>
@@ -986,6 +1067,12 @@
   </si>
   <si>
     <t>463.5</t>
+  </si>
+  <si>
+    <t>438.4</t>
+  </si>
+  <si>
+    <t>400.7</t>
   </si>
   <si>
     <t>注：按照我国国民经济核算数据修订制度和国际通行做法，在第五次全国经济普查后，对1992年-2023年地区生产总值历史数据进行了系统修订。</t>
@@ -1492,1059 +1579,1059 @@
         <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>224</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>279</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>15</v>
+        <v>311</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" ht="20.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" ht="20.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" ht="20.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
